--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB6DD07-7601-4DCA-BEAC-EBF0CC83E2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FD3CD6-1A6B-4980-B278-7CCA0A281608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="540">
   <si>
     <t>商品名称</t>
   </si>
@@ -1907,6 +1907,70 @@
   </si>
   <si>
     <t>555（双冰）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>芙蓉王（锦绣）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028245777</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028245760</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>芙蓉王（绽放）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028195935</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028195805</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>七匹狼（软灰）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028138536</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028138505</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉溪（细支缤果爆）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028325257</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028325240</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>双喜（春天.咖路里）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028247375</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028247368</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028339889</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1961,7 +2025,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2034,14 +2098,14 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2358,7 +2422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80C0A3B-2542-45F0-B3D4-3E8698F6D850}">
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3036,7 +3100,9 @@
       <c r="G27" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="H27" s="11"/>
+      <c r="H27" s="11" t="s">
+        <v>539</v>
+      </c>
       <c r="I27" s="12"/>
       <c r="K27" s="10"/>
     </row>
@@ -4908,7 +4974,7 @@
       <c r="G105" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="H105" s="18" t="s">
+      <c r="H105" s="20" t="s">
         <v>426</v>
       </c>
       <c r="I105" s="12"/>
@@ -4999,7 +5065,7 @@
       <c r="I109" s="12"/>
     </row>
     <row r="110" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="19" t="s">
+      <c r="A110" s="18" t="s">
         <v>431</v>
       </c>
       <c r="C110" s="8">
@@ -5017,7 +5083,7 @@
       <c r="I110" s="12"/>
     </row>
     <row r="111" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="19" t="s">
+      <c r="A111" s="18" t="s">
         <v>438</v>
       </c>
       <c r="C111" s="8">
@@ -5492,17 +5558,17 @@
       <c r="A132" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="B132" s="20">
+      <c r="B132" s="19">
         <v>455.8</v>
       </c>
-      <c r="C132" s="20">
+      <c r="C132" s="19">
         <v>550</v>
       </c>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20">
+      <c r="D132" s="19"/>
+      <c r="E132" s="19">
         <v>55</v>
       </c>
-      <c r="F132" s="20"/>
+      <c r="F132" s="19"/>
       <c r="G132" s="11" t="s">
         <v>506</v>
       </c>
@@ -5514,17 +5580,17 @@
       <c r="A133" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="B133" s="20">
+      <c r="B133" s="19">
         <v>129.30000000000001</v>
       </c>
-      <c r="C133" s="20">
+      <c r="C133" s="19">
         <v>150</v>
       </c>
-      <c r="D133" s="20"/>
-      <c r="E133" s="20">
+      <c r="D133" s="19"/>
+      <c r="E133" s="19">
         <v>15</v>
       </c>
-      <c r="F133" s="20"/>
+      <c r="F133" s="19"/>
       <c r="G133" s="11" t="s">
         <v>509</v>
       </c>
@@ -5536,17 +5602,17 @@
       <c r="A134" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="B134" s="20">
+      <c r="B134" s="19">
         <v>225</v>
       </c>
-      <c r="C134" s="20">
+      <c r="C134" s="19">
         <v>260</v>
       </c>
-      <c r="D134" s="20"/>
-      <c r="E134" s="20">
+      <c r="D134" s="19"/>
+      <c r="E134" s="19">
         <v>26</v>
       </c>
-      <c r="F134" s="20"/>
+      <c r="F134" s="19"/>
       <c r="G134" s="11" t="s">
         <v>512</v>
       </c>
@@ -5558,17 +5624,17 @@
       <c r="A135" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="B135" s="20">
+      <c r="B135" s="19">
         <v>175</v>
       </c>
-      <c r="C135" s="20">
+      <c r="C135" s="19">
         <v>200</v>
       </c>
-      <c r="D135" s="20"/>
-      <c r="E135" s="20">
+      <c r="D135" s="19"/>
+      <c r="E135" s="19">
         <v>20</v>
       </c>
-      <c r="F135" s="20"/>
+      <c r="F135" s="19"/>
       <c r="G135" s="11" t="s">
         <v>515</v>
       </c>
@@ -5580,17 +5646,17 @@
       <c r="A136" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="B136" s="20">
+      <c r="B136" s="19">
         <v>678</v>
       </c>
-      <c r="C136" s="20">
+      <c r="C136" s="19">
         <v>800</v>
       </c>
-      <c r="D136" s="20"/>
-      <c r="E136" s="20">
+      <c r="D136" s="19"/>
+      <c r="E136" s="19">
         <v>80</v>
       </c>
-      <c r="F136" s="20"/>
+      <c r="F136" s="19"/>
       <c r="G136" s="11" t="s">
         <v>518</v>
       </c>
@@ -5602,23 +5668,193 @@
       <c r="A137" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="B137" s="20">
+      <c r="B137" s="19">
         <v>271.07</v>
       </c>
-      <c r="C137" s="20">
+      <c r="C137" s="19">
         <v>320</v>
       </c>
-      <c r="D137" s="20"/>
-      <c r="E137" s="20">
+      <c r="D137" s="19"/>
+      <c r="E137" s="19">
         <v>32</v>
       </c>
-      <c r="F137" s="20"/>
+      <c r="F137" s="19"/>
       <c r="G137" s="11" t="s">
         <v>521</v>
       </c>
       <c r="H137" s="11" t="s">
         <v>522</v>
       </c>
+    </row>
+    <row r="138" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B138" s="19">
+        <v>381.6</v>
+      </c>
+      <c r="C138" s="19">
+        <v>500</v>
+      </c>
+      <c r="D138" s="19"/>
+      <c r="E138" s="19">
+        <v>50</v>
+      </c>
+      <c r="F138" s="19"/>
+      <c r="G138" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B139" s="19">
+        <v>300</v>
+      </c>
+      <c r="C139" s="19">
+        <v>350</v>
+      </c>
+      <c r="D139" s="19"/>
+      <c r="E139" s="19">
+        <v>35</v>
+      </c>
+      <c r="F139" s="19"/>
+      <c r="G139" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="B140" s="19">
+        <v>185.5</v>
+      </c>
+      <c r="C140" s="19">
+        <v>210</v>
+      </c>
+      <c r="D140" s="19"/>
+      <c r="E140" s="19">
+        <v>21</v>
+      </c>
+      <c r="F140" s="19"/>
+      <c r="G140" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B141" s="19">
+        <v>225</v>
+      </c>
+      <c r="C141" s="19">
+        <v>260</v>
+      </c>
+      <c r="D141" s="19"/>
+      <c r="E141" s="19">
+        <v>26</v>
+      </c>
+      <c r="F141" s="19"/>
+      <c r="G141" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B142" s="19">
+        <v>225</v>
+      </c>
+      <c r="C142" s="19">
+        <v>260</v>
+      </c>
+      <c r="D142" s="19"/>
+      <c r="E142" s="19">
+        <v>26</v>
+      </c>
+      <c r="F142" s="19"/>
+      <c r="G142" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="H142" s="11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="6"/>
+      <c r="B143" s="19"/>
+      <c r="C143" s="19"/>
+      <c r="D143" s="19"/>
+      <c r="E143" s="19"/>
+      <c r="F143" s="19"/>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
+    </row>
+    <row r="144" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="6"/>
+      <c r="B144" s="19"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="19"/>
+      <c r="E144" s="19"/>
+      <c r="F144" s="19"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+    </row>
+    <row r="145" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="6"/>
+      <c r="B145" s="19"/>
+      <c r="C145" s="19"/>
+      <c r="D145" s="19"/>
+      <c r="E145" s="19"/>
+      <c r="F145" s="19"/>
+      <c r="G145" s="11"/>
+      <c r="H145" s="11"/>
+    </row>
+    <row r="146" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="6"/>
+      <c r="B146" s="19"/>
+      <c r="C146" s="19"/>
+      <c r="D146" s="19"/>
+      <c r="E146" s="19"/>
+      <c r="F146" s="19"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+    </row>
+    <row r="147" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="6"/>
+      <c r="B147" s="19"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="19"/>
+      <c r="E147" s="19"/>
+      <c r="F147" s="19"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
+    </row>
+    <row r="148" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="6"/>
+      <c r="B148" s="19"/>
+      <c r="C148" s="19"/>
+      <c r="D148" s="19"/>
+      <c r="E148" s="19"/>
+      <c r="F148" s="19"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FD3CD6-1A6B-4980-B278-7CCA0A281608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436E96B0-553C-427C-801C-197D8E59CADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="552">
   <si>
     <t>商品名称</t>
   </si>
@@ -1971,6 +1971,54 @@
   </si>
   <si>
     <t>6901028339889</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京（大观园爆冰）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028112505</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028112499</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄山（红方印金细支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028088060</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028088077</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉溪（创客）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028325103</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028325097</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>芙蓉王（品悦细支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028278263</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028278256</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5797,44 +5845,92 @@
       </c>
     </row>
     <row r="143" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="6"/>
-      <c r="B143" s="19"/>
-      <c r="C143" s="19"/>
+      <c r="A143" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B143" s="19">
+        <v>263</v>
+      </c>
+      <c r="C143" s="19">
+        <v>300</v>
+      </c>
       <c r="D143" s="19"/>
-      <c r="E143" s="19"/>
+      <c r="E143" s="19">
+        <v>30</v>
+      </c>
       <c r="F143" s="19"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
+      <c r="G143" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="144" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="6"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="19"/>
+      <c r="A144" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B144" s="19">
+        <v>263</v>
+      </c>
+      <c r="C144" s="19">
+        <v>300</v>
+      </c>
       <c r="D144" s="19"/>
-      <c r="E144" s="19"/>
+      <c r="E144" s="19">
+        <v>30</v>
+      </c>
       <c r="F144" s="19"/>
-      <c r="G144" s="11"/>
-      <c r="H144" s="11"/>
+      <c r="G144" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="145" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="6"/>
-      <c r="B145" s="19"/>
-      <c r="C145" s="19"/>
+      <c r="A145" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B145" s="19">
+        <v>175</v>
+      </c>
+      <c r="C145" s="19">
+        <v>200</v>
+      </c>
       <c r="D145" s="19"/>
-      <c r="E145" s="19"/>
+      <c r="E145" s="19">
+        <v>20</v>
+      </c>
       <c r="F145" s="19"/>
-      <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
+      <c r="G145" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="146" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="6"/>
-      <c r="B146" s="19"/>
-      <c r="C146" s="19"/>
+      <c r="A146" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B146" s="19">
+        <v>225</v>
+      </c>
+      <c r="C146" s="19">
+        <v>260</v>
+      </c>
       <c r="D146" s="19"/>
-      <c r="E146" s="19"/>
+      <c r="E146" s="19">
+        <v>26</v>
+      </c>
       <c r="F146" s="19"/>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
+      <c r="G146" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="H146" s="11" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="147" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6"/>
